--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.43074</v>
+        <v>16.5788</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75008</v>
+        <v>16.80549</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2968</v>
+        <v>16.70649</v>
       </c>
       <c r="F2" t="n">
-        <v>41.93602</v>
+        <v>41.21107</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05086</v>
+        <v>0.05112</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80314</v>
+        <v>1.76864</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.57717</v>
+        <v>16.91599</v>
       </c>
       <c r="D3" t="n">
-        <v>16.09573</v>
+        <v>16.50577</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46054</v>
+        <v>16.55384</v>
       </c>
       <c r="F3" t="n">
-        <v>42.5932</v>
+        <v>4235.64</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05066</v>
+        <v>0.05071</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79633</v>
+        <v>1.78388</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.1676</v>
+        <v>16.72691</v>
       </c>
       <c r="D4" t="n">
-        <v>16.51494</v>
+        <v>16.274</v>
       </c>
       <c r="E4" t="n">
-        <v>16.69698</v>
+        <v>16.65174</v>
       </c>
       <c r="F4" t="n">
-        <v>42.32597</v>
+        <v>42.51777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0509</v>
+        <v>0.0497</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83061</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.61726</v>
+        <v>16.71865</v>
       </c>
       <c r="D5" t="n">
-        <v>16.52608</v>
+        <v>16.24072</v>
       </c>
       <c r="E5" t="n">
-        <v>16.32474</v>
+        <v>16.64766</v>
       </c>
       <c r="F5" t="n">
-        <v>41.67644</v>
+        <v>42.43389</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05021</v>
+        <v>0.0502</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79292</v>
+        <v>1.8069</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.45462</v>
+        <v>17.08318</v>
       </c>
       <c r="D6" t="n">
-        <v>16.54991</v>
+        <v>16.41169</v>
       </c>
       <c r="E6" t="n">
-        <v>16.44309</v>
+        <v>16.57804</v>
       </c>
       <c r="F6" t="n">
-        <v>42.14732</v>
+        <v>42.33106</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0495</v>
+        <v>0.05058</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81832</v>
+        <v>1.81385</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.54435</v>
+        <v>16.81323</v>
       </c>
       <c r="D7" t="n">
-        <v>16.65788</v>
+        <v>16.64242</v>
       </c>
       <c r="E7" t="n">
-        <v>16.71834</v>
+        <v>16.65236</v>
       </c>
       <c r="F7" t="n">
-        <v>41.52657</v>
+        <v>42.99197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05026</v>
+        <v>0.05036</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8015</v>
+        <v>1.79623</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.63515</v>
+        <v>16.81753</v>
       </c>
       <c r="D8" t="n">
-        <v>16.76415</v>
+        <v>16.36198</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55352</v>
+        <v>16.64869</v>
       </c>
       <c r="F8" t="n">
-        <v>42.44661</v>
+        <v>41.4298</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05063</v>
+        <v>0.05213</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85578</v>
+        <v>1.82815</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.42599</v>
+        <v>16.6753</v>
       </c>
       <c r="D9" t="n">
-        <v>16.562</v>
+        <v>16.52858</v>
       </c>
       <c r="E9" t="n">
-        <v>16.81271</v>
+        <v>16.65502</v>
       </c>
       <c r="F9" t="n">
-        <v>42.40827</v>
+        <v>42.46994</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05135</v>
+        <v>0.04956</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79793</v>
+        <v>1.77491</v>
       </c>
     </row>
     <row r="10">
@@ -650,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.9872</v>
+        <v>16.78135</v>
       </c>
       <c r="D10" t="n">
-        <v>16.81411</v>
+        <v>16.48209</v>
       </c>
       <c r="E10" t="n">
-        <v>16.56968</v>
+        <v>16.66017</v>
       </c>
       <c r="F10" t="n">
-        <v>43.14708</v>
+        <v>42.06453</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05072</v>
+        <v>0.04973</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82465</v>
+        <v>1.80559</v>
       </c>
     </row>
     <row r="11">
@@ -692,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6035700000000001</v>
+        <v>0.60599</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09598</v>
+        <v>1.12176</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60193</v>
+        <v>0.60424</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10635</v>
+        <v>1.11349</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.61242</v>
+        <v>0.6076</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0935</v>
+        <v>1.09461</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5954</v>
+        <v>0.59673</v>
       </c>
       <c r="D15" t="n">
-        <v>1.09951</v>
+        <v>1.11699</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60807</v>
+        <v>0.60777</v>
       </c>
       <c r="D16" t="n">
-        <v>1.07817</v>
+        <v>1.12812</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59082</v>
+        <v>0.59495</v>
       </c>
       <c r="D17" t="n">
-        <v>1.13318</v>
+        <v>1.10279</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60929</v>
+        <v>0.61797</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10789</v>
+        <v>1.13301</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60066</v>
+        <v>0.59815</v>
       </c>
       <c r="D19" t="n">
-        <v>1.10306</v>
+        <v>1.1191</v>
       </c>
     </row>
     <row r="20">
@@ -796,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.61482</v>
+        <v>0.59362</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11078</v>
+        <v>1.09931</v>
       </c>
     </row>
     <row r="21">
@@ -856,28 +866,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.74675</v>
+        <v>0.74688</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07901</v>
+        <v>0.08173999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60737</v>
+        <v>0.60795</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95381</v>
+        <v>0.94763</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11016</v>
+        <v>0.10735</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00762</v>
+        <v>0.0076</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09266000000000001</v>
+        <v>0.09135</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12531</v>
+        <v>0.12494</v>
       </c>
     </row>
     <row r="23">
@@ -887,28 +897,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.73892</v>
+        <v>0.74757</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08162999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60317</v>
+        <v>0.58179</v>
       </c>
       <c r="F23" t="n">
-        <v>0.94824</v>
+        <v>0.95804</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10874</v>
+        <v>0.10931</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00755</v>
+        <v>0.00748</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09363</v>
+        <v>0.09218999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12434</v>
+        <v>0.12704</v>
       </c>
     </row>
     <row r="24">
@@ -918,28 +928,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75202</v>
+        <v>0.75553</v>
       </c>
       <c r="D24" t="n">
-        <v>0.081</v>
+        <v>0.08173</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5945</v>
+        <v>0.59884</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95769</v>
+        <v>0.95439</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10711</v>
+        <v>0.11245</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0076</v>
+        <v>0.00745</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09128</v>
+        <v>0.09344</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12548</v>
+        <v>0.12679</v>
       </c>
     </row>
     <row r="25">
@@ -949,28 +959,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.73799</v>
+        <v>0.74392</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07998</v>
+        <v>0.07928</v>
       </c>
       <c r="E25" t="n">
-        <v>0.59655</v>
+        <v>0.60204</v>
       </c>
       <c r="F25" t="n">
-        <v>0.94865</v>
+        <v>0.95126</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10812</v>
+        <v>0.10866</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00764</v>
+        <v>0.00738</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09205000000000001</v>
+        <v>0.09264</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12686</v>
+        <v>0.12716</v>
       </c>
     </row>
     <row r="26">
@@ -980,28 +990,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.73838</v>
+        <v>0.7285199999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08078</v>
+        <v>0.07983999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.59941</v>
+        <v>0.6059099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.95502</v>
+        <v>0.94609</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10761</v>
+        <v>0.10858</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00745</v>
+        <v>0.00746</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09192</v>
+        <v>0.095</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12882</v>
+        <v>0.12506</v>
       </c>
     </row>
     <row r="27">
@@ -1011,28 +1021,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7340100000000001</v>
+        <v>0.74734</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07994999999999999</v>
+        <v>0.07943</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6096200000000001</v>
+        <v>0.60214</v>
       </c>
       <c r="F27" t="n">
-        <v>0.97226</v>
+        <v>0.94694</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10918</v>
+        <v>0.10803</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00758</v>
+        <v>0.00775</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09163</v>
+        <v>0.09317</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12504</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="28">
@@ -1042,28 +1052,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74096</v>
+        <v>0.74926</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07869</v>
+        <v>0.07972</v>
       </c>
       <c r="E28" t="n">
-        <v>0.59689</v>
+        <v>0.60384</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96012</v>
+        <v>0.94708</v>
       </c>
       <c r="G28" t="n">
-        <v>0.10994</v>
+        <v>0.11136</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00739</v>
+        <v>0.00757</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09053</v>
+        <v>0.09311999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12518</v>
+        <v>0.12677</v>
       </c>
     </row>
     <row r="29">
@@ -1073,28 +1083,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74756</v>
+        <v>0.73164</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08079</v>
+        <v>0.07897</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60716</v>
+        <v>0.61603</v>
       </c>
       <c r="F29" t="n">
-        <v>0.97524</v>
+        <v>0.9463200000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10786</v>
+        <v>0.10688</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00763</v>
+        <v>0.0076</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09291000000000001</v>
+        <v>0.09166000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12636</v>
+        <v>0.12686</v>
       </c>
     </row>
     <row r="30">
@@ -1104,28 +1114,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74385</v>
+        <v>0.75153</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07869</v>
+        <v>0.07892</v>
       </c>
       <c r="E30" t="n">
-        <v>0.58683</v>
+        <v>0.60081</v>
       </c>
       <c r="F30" t="n">
-        <v>0.96754</v>
+        <v>0.94822</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11058</v>
+        <v>0.10603</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00767</v>
+        <v>0.00766</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09296</v>
+        <v>0.09336999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12514</v>
+        <v>0.12857</v>
       </c>
     </row>
   </sheetData>
